--- a/workbooks/07 Shortcuts 4 - Organize and Analyze.xlsx
+++ b/workbooks/07 Shortcuts 4 - Organize and Analyze.xlsx
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="1130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="1131">
   <si>
     <t>Challenge</t>
   </si>
@@ -3258,58 +3258,61 @@
     <t>The same keys that open a dropdown.</t>
   </si>
   <si>
+    <t>Which move is this? On a header with a filter button, open its filter menu.</t>
+  </si>
+  <si>
+    <t>S4-4 Data Wrangler T3</t>
+  </si>
+  <si>
+    <t>T for Table.</t>
+  </si>
+  <si>
+    <t>Which keys turn a range into a Table?</t>
+  </si>
+  <si>
+    <t>S4-4 Data Wrangler T4</t>
+  </si>
+  <si>
+    <t>Alt, A, S, then A for ascending.</t>
+  </si>
+  <si>
+    <t>Which KeyTips sort A to Z?</t>
+  </si>
+  <si>
+    <t>S4-4 Data Wrangler T5</t>
+  </si>
+  <si>
+    <t>Alt, A, S, then D for descending.</t>
+  </si>
+  <si>
+    <t>Which KeyTips sort Z to A?</t>
+  </si>
+  <si>
+    <t>S4-4 Data Wrangler T6</t>
+  </si>
+  <si>
+    <t>Alt plus F1.</t>
+  </si>
+  <si>
+    <t>Which keys insert an instant chart on the sheet?</t>
+  </si>
+  <si>
+    <t>▶ Open S4-4 Arena (or press Ctrl+PgDn)</t>
+  </si>
+  <si>
+    <t>S4-4 Data Wrangler C1</t>
+  </si>
+  <si>
+    <t>CTRL+SHIFT+L</t>
+  </si>
+  <si>
+    <t>SHIFT+CTRL+L</t>
+  </si>
+  <si>
+    <t>S4-4 Data Wrangler C2</t>
+  </si>
+  <si>
     <t>Which keys open the filter menu of a header cell?</t>
-  </si>
-  <si>
-    <t>S4-4 Data Wrangler T3</t>
-  </si>
-  <si>
-    <t>T for Table.</t>
-  </si>
-  <si>
-    <t>Which keys turn a range into a Table?</t>
-  </si>
-  <si>
-    <t>S4-4 Data Wrangler T4</t>
-  </si>
-  <si>
-    <t>Alt, A, S, then A for ascending.</t>
-  </si>
-  <si>
-    <t>Which KeyTips sort A to Z?</t>
-  </si>
-  <si>
-    <t>S4-4 Data Wrangler T5</t>
-  </si>
-  <si>
-    <t>Alt, A, S, then D for descending.</t>
-  </si>
-  <si>
-    <t>Which KeyTips sort Z to A?</t>
-  </si>
-  <si>
-    <t>S4-4 Data Wrangler T6</t>
-  </si>
-  <si>
-    <t>Alt plus F1.</t>
-  </si>
-  <si>
-    <t>Which keys insert an instant chart on the sheet?</t>
-  </si>
-  <si>
-    <t>▶ Open S4-4 Arena (or press Ctrl+PgDn)</t>
-  </si>
-  <si>
-    <t>S4-4 Data Wrangler C1</t>
-  </si>
-  <si>
-    <t>CTRL+SHIFT+L</t>
-  </si>
-  <si>
-    <t>SHIFT+CTRL+L</t>
-  </si>
-  <si>
-    <t>S4-4 Data Wrangler C2</t>
   </si>
   <si>
     <t>S4-4 Data Wrangler C3</t>
@@ -4768,7 +4771,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4778,12 +4781,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -4793,32 +4796,32 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -4828,30 +4831,30 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>762</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C13" s="9" cm="1" t="str">
         <f t="array" ref="C13">SUM('S4-1 Construction Crew'!$G$14:$G$42)&amp;" / 220"</f>
@@ -4866,15 +4869,15 @@
         <v>NEW</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C14" s="9" cm="1" t="str">
         <f t="array" ref="C14">SUM('S4-2 Sheet Master'!$G$18:$G$53)&amp;" / 290"</f>
@@ -4889,15 +4892,15 @@
         <v>NEW</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C15" s="9" cm="1" t="str">
         <f t="array" ref="C15">SUM('S4-3 Detective'!$G$12:$G$35)&amp;" / 170"</f>
@@ -4912,15 +4915,15 @@
         <v>NEW</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C16" s="9" cm="1" t="str">
         <f t="array" ref="C16">SUM('S4-4 Data Wrangler'!$G$16:$G$47)&amp;" / 250"</f>
@@ -4935,15 +4938,15 @@
         <v>NEW</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C17" s="9" cm="1" t="str">
         <f t="array" ref="C17">SUM(Boss!$G$14:$G$33)&amp;" / 160"</f>
@@ -4958,12 +4961,12 @@
         <v>LOCKED</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="7" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B19" s="12" cm="1" t="str">
         <f t="array" ref="B19">(SUM('S4-1 Construction Crew'!$G$14:$G$42)+SUM('S4-2 Sheet Master'!$G$18:$G$53)+SUM('S4-3 Detective'!$G$12:$G$35)+SUM('S4-4 Data Wrangler'!$G$16:$G$47)+SUM(Boss!$G$14:$G$33))&amp;" / 1090"</f>
@@ -4972,19 +4975,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="7" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B20" s="12" cm="1" t="str">
         <f t="array" ref="B20">_xlfn.LET(_xlpm.p,(SUM('S4-1 Construction Crew'!$G$14:$G$42)+SUM('S4-2 Sheet Master'!$G$18:$G$53)+SUM('S4-3 Detective'!$G$12:$G$35)+SUM('S4-4 Data Wrangler'!$G$16:$G$47)+SUM(Boss!$G$14:$G$33))/1090,IF(AND(_xlpm.p&gt;=1,ISNUMBER(Boss!$C$8),Boss!$C$8&lt;=12),"S",IF(_xlpm.p&gt;=0.9,"A",IF(_xlpm.p&gt;=0.75,"B",IF(_xlpm.p&gt;=0.5,"C","D")))))</f>
         <v>D</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="7" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B21" s="12" cm="1" t="str">
         <f t="array" ref="B21">IF(ISNUMBER(Boss!$C$8),Boss!$C$8&amp;" min (par 12)","—")</f>
@@ -4993,7 +4996,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="7" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B22" s="12" cm="1" t="str">
         <f t="array" ref="B22">IFERROR(INDEX($A$13:$A$16,MATCH("☆☆☆",$D$13:$D$16,0))&amp;" "&amp;INDEX($B$13:$B$16,MATCH("☆☆☆",$D$13:$D$16,0)),IF(Boss!$C$10="OPEN","the Boss","All clear! Aim for rank S"))</f>
@@ -5002,7 +5005,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="13" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
   </sheetData>
@@ -5548,7 +5551,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5559,7 +5562,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -5578,7 +5581,7 @@
     </row>
     <row r="5" spans="1:7" ht="22" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -5589,19 +5592,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C6" s="28"/>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C7" s="28"/>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" s="7" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C8" s="29" cm="1" t="str">
         <f t="array" ref="C8">IF(OR(C6="",C7=""),"",ROUND(MOD(C7-C6,1)*1440,0))</f>
@@ -5610,7 +5613,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="7" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C9" s="29">
         <v>12</v>
@@ -5618,7 +5621,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="B10" s="7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C10" s="12" cm="1" t="str">
         <f t="array" ref="C10">IF(AND(SUM('S4-1 Construction Crew'!$G$14:$G$42)&gt;=220*0.5,SUM('S4-2 Sheet Master'!$G$18:$G$53)&gt;=290*0.5,SUM('S4-3 Detective'!$G$12:$G$35)&gt;=170*0.5,SUM('S4-4 Data Wrangler'!$G$16:$G$47)&gt;=250*0.5),"OPEN","LOCKED")</f>
@@ -5631,7 +5634,7 @@
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -5665,7 +5668,7 @@
     </row>
     <row r="14" spans="1:7" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B14" s="30" cm="1" t="str">
         <f t="array" ref="B14">IF($C$10="OPEN","Which keys turn filter buttons on and off?  (from S4-4 Data Wrangler)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5688,7 +5691,7 @@
     </row>
     <row r="15" spans="1:7" ht="35.5" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B15" s="30" cm="1" t="str">
         <f t="array" ref="B15">IF($C$10="OPEN","Which keys open the filter menu of a header cell?  (from S4-4 Data Wrangler)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5711,7 +5714,7 @@
     </row>
     <row r="16" spans="1:7" ht="35.5" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B16" s="30" cm="1" t="str">
         <f t="array" ref="B16">IF($C$10="OPEN","Which keys turn a range into a Table?  (from S4-4 Data Wrangler)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5734,7 +5737,7 @@
     </row>
     <row r="17" spans="1:7" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B17" s="30" cm="1" t="str">
         <f t="array" ref="B17">IF($C$10="OPEN","Which KeyTips sort A to Z?  (from S4-4 Data Wrangler)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5757,7 +5760,7 @@
     </row>
     <row r="18" spans="1:7" ht="35.5" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B18" s="30" cm="1" t="str">
         <f t="array" ref="B18">IF($C$10="OPEN","Which KeyTips sort Z to A?  (from S4-4 Data Wrangler)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5780,7 +5783,7 @@
     </row>
     <row r="19" spans="1:7" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B19" s="30" cm="1" t="str">
         <f t="array" ref="B19">IF($C$10="OPEN","Which keys insert an instant chart on the sheet?  (from S4-4 Data Wrangler)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5803,7 +5806,7 @@
     </row>
     <row r="20" spans="1:7" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B20" s="30" cm="1" t="str">
         <f t="array" ref="B20">IF($C$10="OPEN","Which keys insert cells or rows?  (from S4-1 Construction Crew)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5826,7 +5829,7 @@
     </row>
     <row r="21" spans="1:7" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B21" s="30" cm="1" t="str">
         <f t="array" ref="B21">IF($C$10="OPEN","Which keys delete the selected cells or rows?  (from S4-1 Construction Crew)","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5849,7 +5852,7 @@
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -5860,7 +5863,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="B24" s="11" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -5888,14 +5891,14 @@
     </row>
     <row r="26" spans="1:7" ht="35.5" customHeight="1">
       <c r="A26" s="18" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B26" s="30" cm="1" t="str">
         <f t="array" ref="B26">IF($C$10="OPEN","Filter the table at B5 to show only West (Ctrl+Shift+L, then Alt+↓ on Region).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D26" s="21" cm="1" t="str">
         <f t="array" ref="D26">IF($C$10="OPEN",IF(IFERROR(AND(SUBTOTAL(103,'Boss Arena'!$C$6:$C$25)=5,SUMPRODUCT(SUBTOTAL(103,OFFSET('Boss Arena'!$C$6,ROW('Boss Arena'!$C$6:$C$25)-ROW('Boss Arena'!$C$6),0))*('Boss Arena'!$C$6:$C$25&lt;&gt;"West"))=0),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -5913,14 +5916,14 @@
     </row>
     <row r="27" spans="1:7" ht="35.5" customHeight="1">
       <c r="A27" s="18" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B27" s="30" cm="1" t="str">
         <f t="array" ref="B27">IF($C$10="OPEN","Sort the table at B30 by Player name A→Z: click a name, then Alt, A, S, A.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D27" s="21" cm="1" t="str">
         <f t="array" ref="D27">IF($C$10="OPEN",IF(IFERROR(AND(SUMPRODUCT(--('Boss Arena'!$B$31:$B$39&gt;'Boss Arena'!$B$32:$B$40))=0,SUMPRODUCT(--(_xlfn.XLOOKUP('Boss Arena'!$B$31:$B$40,{"Ann","Bo","Cy","Di","Ed","Flo","Gil","Hu","Ida","Jay"},{40,90,70,10,55,85,25,65,95,35})='Boss Arena'!$C$31:$C$40))=10),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -5938,7 +5941,7 @@
     </row>
     <row r="28" spans="1:7" ht="35.5" customHeight="1">
       <c r="A28" s="18" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B28" s="30" cm="1" t="str">
         <f t="array" ref="B28">IF($C$10="OPEN","Use Ctrl+F to find Zircon. Type its Stock (the cell to its right).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
@@ -5961,14 +5964,14 @@
     </row>
     <row r="29" spans="1:7" ht="35.5" customHeight="1">
       <c r="A29" s="18" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B29" s="30" cm="1" t="str">
         <f t="array" ref="B29">IF($C$10="OPEN","Use Ctrl+H to replace every TBD in the Status column with Pending (Replace All).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D29" s="21" cm="1" t="str">
         <f t="array" ref="D29">IF($C$10="OPEN",IF(IFERROR(AND(COUNTIF('Boss Arena'!$D$46:$D$105,"TBD")=0,COUNTIF('Boss Arena'!$D$46:$D$105,"Pending")=9),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -5986,14 +5989,14 @@
     </row>
     <row r="30" spans="1:7" ht="35.5" customHeight="1">
       <c r="A30" s="18" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B30" s="30" cm="1" t="str">
         <f t="array" ref="B30">IF($C$10="OPEN","Hide both HIDDEN rows in the HIDE LIST (Shift+Space, then Ctrl+9). Press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="D30" s="21" cm="1" t="str">
         <f t="array" ref="D30">IF($C$10="OPEN",IF(IFERROR(AND(SUMPRODUCT(SUBTOTAL(103,OFFSET('Boss Arena'!$B$111,ROW('Boss Arena'!$B$111:$B$118)-ROW('Boss Arena'!$B$111),0))*('Boss Arena'!$B$111:$B$118="HIDDEN"))=0,SUBTOTAL(103,'Boss Arena'!$B$111:$B$118)=6),FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -6011,14 +6014,14 @@
     </row>
     <row r="31" spans="1:7" ht="35.5" customHeight="1">
       <c r="A31" s="18" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B31" s="30" cm="1" t="str">
         <f t="array" ref="B31">IF($C$10="OPEN","Insert two blank rows above INSERT ABOVE (Shift+Space, Shift+↓, Ctrl+Shift++).","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D31" s="21" cm="1" t="str">
         <f t="array" ref="D31">IF($C$10="OPEN",IF(IFERROR(MATCH("INSERT ABOVE",'Boss Arena'!$B:$B,0)-MATCH("ROW ABOVE",'Boss Arena'!$B:$B,0)=3,FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -6036,14 +6039,14 @@
     </row>
     <row r="32" spans="1:7" ht="35.5" customHeight="1">
       <c r="A32" s="18" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B32" s="30" cm="1" t="str">
         <f t="array" ref="B32">IF($C$10="OPEN","Delete the three REMOVE rows in LIST: select each with Shift+Space and press Ctrl+-.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D32" s="21" cm="1" t="str">
         <f t="array" ref="D32">IF($C$10="OPEN",IF(IFERROR(AND(COUNTIF('Boss Arena'!$B:$B,"REMOVE")=0,COUNTIF('Boss Arena'!$B:$B,"KEEP")=5),FALSE),"✔ CLEAR","· not yet"),"LOCKED")</f>
@@ -6061,14 +6064,14 @@
     </row>
     <row r="33" spans="1:7" ht="35.5" customHeight="1">
       <c r="A33" s="18" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B33" s="30" cm="1" t="str">
         <f t="array" ref="B33">IF($C$10="OPEN","Insert a new worksheet with Shift+F11, come back and press F9.","LOCKED · earn ★ on every stage to open the Boss gate")</f>
         <v>LOCKED · earn ★ on every stage to open the Boss gate</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D33" s="21" cm="1" t="str">
         <f t="array" ref="D33">IF($C$10="OPEN",IF(IFERROR(_xlfn.SHEETS()&gt;14,FALSE),"✔ CLEAR","· not yet · press F9"),"LOCKED")</f>
@@ -6185,7 +6188,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -6198,10 +6201,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -6621,718 +6624,718 @@
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="27" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C45" s="27" t="s">
         <v>344</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="5" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C46" s="5">
         <v>3</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="47" spans="2:4">
       <c r="B47" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C47" s="5">
         <v>20</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="48" spans="2:4">
       <c r="B48" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C48" s="5">
         <v>37</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="49" spans="2:4">
       <c r="B49" s="5" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C49" s="5">
         <v>54</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="50" spans="2:4">
       <c r="B50" s="5" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C50" s="5">
         <v>71</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="51" spans="2:4">
       <c r="B51" s="5" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C51" s="5">
         <v>18</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="52" spans="2:4">
       <c r="B52" s="5" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C52" s="5">
         <v>35</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="53" spans="2:4">
       <c r="B53" s="5" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C53" s="5">
         <v>52</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="54" spans="2:4">
       <c r="B54" s="5" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C54" s="5">
         <v>69</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="55" spans="2:4">
       <c r="B55" s="5" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C55" s="5">
         <v>16</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="56" spans="2:4">
       <c r="B56" s="5" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C56" s="5">
         <v>33</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="57" spans="2:4">
       <c r="B57" s="5" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C57" s="5">
         <v>50</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="58" spans="2:4">
       <c r="B58" s="5" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C58" s="5">
         <v>67</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="59" spans="2:4">
       <c r="B59" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C59" s="5">
         <v>14</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="60" spans="2:4">
       <c r="B60" s="5" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C60" s="5">
         <v>31</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="61" spans="2:4">
       <c r="B61" s="5" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C61" s="5">
         <v>48</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="62" spans="2:4">
       <c r="B62" s="5" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C62" s="5">
         <v>65</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="63" spans="2:4">
       <c r="B63" s="5" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C63" s="5">
         <v>12</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="64" spans="2:4">
       <c r="B64" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C64" s="5">
         <v>29</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="65" spans="2:4">
       <c r="B65" s="5" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C65" s="5">
         <v>46</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="66" spans="2:4">
       <c r="B66" s="5" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C66" s="5">
         <v>63</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="67" spans="2:4">
       <c r="B67" s="5" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C67" s="5">
         <v>10</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="68" spans="2:4">
       <c r="B68" s="5" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C68" s="5">
         <v>27</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="69" spans="2:4">
       <c r="B69" s="5" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C69" s="5">
         <v>44</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="70" spans="2:4">
       <c r="B70" s="5" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C70" s="5">
         <v>61</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="71" spans="2:4">
       <c r="B71" s="5" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C71" s="5">
         <v>8</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="72" spans="2:4">
       <c r="B72" s="5" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C72" s="5">
         <v>25</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="73" spans="2:4">
       <c r="B73" s="5" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C73" s="5">
         <v>42</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="74" spans="2:4">
       <c r="B74" s="5" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C74" s="5">
         <v>59</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="75" spans="2:4">
       <c r="B75" s="5" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C75" s="5">
         <v>6</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="76" spans="2:4">
       <c r="B76" s="5" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C76" s="5">
         <v>23</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="5" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C77" s="5">
         <v>40</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="78" spans="2:4">
       <c r="B78" s="5" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C78" s="5">
         <v>57</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="79" spans="2:4">
       <c r="B79" s="5" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C79" s="5">
         <v>4</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="80" spans="2:4">
       <c r="B80" s="5" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C80" s="5">
         <v>21</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="81" spans="2:4">
       <c r="B81" s="5" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C81" s="5">
         <v>38</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="82" spans="2:4">
       <c r="B82" s="5" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C82" s="5">
         <v>55</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="83" spans="2:4">
       <c r="B83" s="5" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C83" s="5">
         <v>72</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="84" spans="2:4">
       <c r="B84" s="5" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C84" s="5">
         <v>19</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="85" spans="2:4">
       <c r="B85" s="5" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C85" s="5">
         <v>36</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="86" spans="2:4">
       <c r="B86" s="5" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C86" s="5">
         <v>53</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="87" spans="2:4">
       <c r="B87" s="5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C87" s="5">
         <v>70</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="88" spans="2:4">
       <c r="B88" s="5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C88" s="5">
         <v>17</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="89" spans="2:4">
       <c r="B89" s="5" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C89" s="5">
         <v>34</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="90" spans="2:4">
       <c r="B90" s="5" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C90" s="5">
         <v>51</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="91" spans="2:4">
       <c r="B91" s="5" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C91" s="5">
         <v>68</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="92" spans="2:4">
       <c r="B92" s="5" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C92" s="5">
         <v>15</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="93" spans="2:4">
       <c r="B93" s="5" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C93" s="5">
         <v>32</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="94" spans="2:4">
       <c r="B94" s="5" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C94" s="5">
         <v>49</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="95" spans="2:4">
       <c r="B95" s="5" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C95" s="5">
         <v>66</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="96" spans="2:4">
       <c r="B96" s="5" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C96" s="5">
         <v>13</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="97" spans="2:4">
       <c r="B97" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C97" s="5">
         <v>30</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="98" spans="2:4">
       <c r="B98" s="5" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C98" s="5">
         <v>47</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="B99" s="5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C99" s="5">
         <v>64</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="100" spans="2:4">
       <c r="B100" s="5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C100" s="5">
         <v>11</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="101" spans="2:4">
       <c r="B101" s="5" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C101" s="5">
         <v>28</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="102" spans="2:4">
       <c r="B102" s="5" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C102" s="5">
         <v>45</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="103" spans="2:4">
       <c r="B103" s="5" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C103" s="5">
         <v>62</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="104" spans="2:4">
       <c r="B104" s="5" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C104" s="5">
         <v>9</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="105" spans="2:4">
       <c r="B105" s="5" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C105" s="5">
         <v>26</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="110" spans="2:4">
       <c r="B110" s="7" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="111" spans="2:4">
       <c r="B111" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="112" spans="2:4">
       <c r="B112" s="5" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="113" spans="2:2">
       <c r="B113" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="114" spans="2:2">
       <c r="B114" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="115" spans="2:2">
       <c r="B115" s="5" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="116" spans="2:2">
       <c r="B116" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="117" spans="2:2">
       <c r="B117" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="118" spans="2:2">
       <c r="B118" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="122" spans="2:2">
@@ -7357,7 +7360,7 @@
     </row>
     <row r="129" spans="2:2">
       <c r="B129" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="130" spans="2:2">
@@ -7367,7 +7370,7 @@
     </row>
     <row r="131" spans="2:2">
       <c r="B131" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="132" spans="2:2">
@@ -7377,7 +7380,7 @@
     </row>
     <row r="133" spans="2:2">
       <c r="B133" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="134" spans="2:2">
@@ -7415,7 +7418,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7423,301 +7426,301 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="35.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>24</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="35.5" customHeight="1">
       <c r="A6" s="18" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="19.75" customHeight="1">
       <c r="A7" s="18" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.75" customHeight="1">
       <c r="A8" s="18" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.75" customHeight="1">
       <c r="A9" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>180</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="35.5" customHeight="1">
       <c r="A10" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>182</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.75" customHeight="1">
       <c r="A11" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="35.5" customHeight="1">
       <c r="A12" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>113</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="19.75" customHeight="1">
       <c r="A13" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>187</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.5" customHeight="1">
       <c r="A14" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>190</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="19.75" customHeight="1">
       <c r="A15" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>128</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="19.75" customHeight="1">
       <c r="A16" s="18" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>195</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35.5" customHeight="1">
       <c r="A17" s="18" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>267</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="19.75" customHeight="1">
       <c r="A18" s="18" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="35.5" customHeight="1">
       <c r="A19" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>786</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="35.5" customHeight="1">
       <c r="A20" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>130</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="35.5" customHeight="1">
       <c r="A21" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>129</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="35.5" customHeight="1">
       <c r="A22" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>122</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="35.5" customHeight="1">
       <c r="A23" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>111</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="35.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>260</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
   </sheetData>
@@ -9285,163 +9288,163 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B88" t="s">
         <v>855</v>
       </c>
       <c r="E88" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F88" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B89" t="s">
         <v>858</v>
       </c>
       <c r="E89" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F89" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G89" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H89" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I89" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J89" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="K89" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L89" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M89" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N89" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="O89" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="P89" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="Q89" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="R89" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="S89" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="T89" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B90" t="s">
         <v>861</v>
       </c>
       <c r="E90" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F90" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G90" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H90" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I90" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J90" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K90" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="L90" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M90" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N90" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="O90" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="P90" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="Q90" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="R90" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="S90" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="T90" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B91" t="s">
         <v>864</v>
       </c>
       <c r="E91" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B92" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B93" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B94" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="E94" t="s">
         <v>333</v>
@@ -9449,7 +9452,7 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B95" t="s">
         <v>849</v>
@@ -9463,7 +9466,7 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B96" t="s">
         <v>852</v>
@@ -9474,144 +9477,144 @@
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B97" t="s">
         <v>855</v>
       </c>
       <c r="E97" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="F97" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B98" t="s">
         <v>858</v>
       </c>
       <c r="E98" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F98" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G98" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H98" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="I98" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J98" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="K98" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L98" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="M98" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N98" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="O98" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="P98" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="Q98" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="R98" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="S98" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="T98" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B99" t="s">
         <v>861</v>
       </c>
       <c r="E99" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F99" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="G99" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H99" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I99" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="J99" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K99" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="L99" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="M99" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="N99" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="O99" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="P99" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="Q99" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="R99" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="S99" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="T99" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B100" t="s">
         <v>864</v>
       </c>
       <c r="E100" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B101" t="s">
         <v>110</v>
@@ -9634,7 +9637,7 @@
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B102" t="s">
         <v>117</v>
@@ -9645,26 +9648,26 @@
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B103" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B104" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B105" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C105">
         <v>17</v>
@@ -9672,39 +9675,39 @@
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B106" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B107" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B108" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B109" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B110" t="s">
         <v>322</v>
@@ -10423,7 +10426,7 @@
         <v>170</v>
       </c>
       <c r="D42" s="21" cm="1" t="str">
-        <f t="array" ref="D42">IF(IFERROR(CELL("width",'S4-1 Arena'!$H$5)=0,FALSE),"✔ CLEAR","· not yet · press F9")</f>
+        <f t="array" ref="D42">IF(IFERROR(INDEX(CELL("width",'S4-1 Arena'!$H$5),1)=0,FALSE),"✔ CLEAR","· not yet · press F9")</f>
         <v>· not yet · press F9</v>
       </c>
       <c r="E42" s="22"/>
@@ -11690,7 +11693,7 @@
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="21" cm="1" t="str">
-        <f t="array" ref="D53">IF('S4-2 Sheet Master'!$C$53="Done","✔ CLEAR · self-check","")</f>
+        <f t="array" ref="D53">IFERROR(IF('S4-2 Sheet Master'!$C$53="Done","✔ CLEAR · self-check",""),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E53" s="22"/>
@@ -17778,7 +17781,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17789,7 +17792,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="26" customHeight="1">
@@ -18388,7 +18391,7 @@
         <v>144</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>853</v>
+        <v>871</v>
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="21" cm="1" t="str">
@@ -18498,10 +18501,10 @@
         <v>163</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="D45" s="21" cm="1" t="str">
         <f t="array" ref="D45">IF(IFERROR(AND(SUBTOTAL(103,'S4-4 Arena'!$C$6:$C$25)=7,SUMPRODUCT(SUBTOTAL(103,OFFSET('S4-4 Arena'!$C$6,ROW('S4-4 Arena'!$C$6:$C$25)-ROW('S4-4 Arena'!$C$6),0))*('S4-4 Arena'!$C$6:$C$25&lt;&gt;"East"))=0),FALSE),"✔ CLEAR","· not yet")</f>
@@ -18522,10 +18525,10 @@
         <v>168</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D46" s="21" cm="1" t="str">
         <f t="array" ref="D46">IF(IFERROR(AND(SUMPRODUCT(--('S4-4 Arena'!$C$31:$C$39&lt;'S4-4 Arena'!$C$32:$C$40))=0,SUMPRODUCT(--(_xlfn.XLOOKUP('S4-4 Arena'!$B$31:$B$40,{"Ann","Bo","Cy","Di","Ed","Flo","Gil","Hu","Ida","Jay"},{40,90,70,10,55,85,25,65,95,35})='S4-4 Arena'!$C$31:$C$40))=10),FALSE),"✔ CLEAR","· not yet")</f>
@@ -18546,11 +18549,11 @@
         <v>323</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="21" cm="1" t="str">
-        <f t="array" ref="D47">IF('S4-4 Data Wrangler'!$C$47="Done","✔ CLEAR · self-check","")</f>
+        <f t="array" ref="D47">IFERROR(IF('S4-4 Data Wrangler'!$C$47="Done","✔ CLEAR · self-check",""),"✘ TRY AGAIN")</f>
         <v/>
       </c>
       <c r="E47" s="22"/>
